--- a/samples/Trial_Balance_UK_Jul-26.xlsx
+++ b/samples/Trial_Balance_UK_Jul-26.xlsx
@@ -450,7 +450,7 @@
         <v>Bank</v>
       </c>
       <c r="D7">
-        <v>54380.64</v>
+        <v>279016.49</v>
       </c>
     </row>
     <row r="8">
@@ -464,7 +464,7 @@
         <v>Cash</v>
       </c>
       <c r="D8">
-        <v>110.82</v>
+        <v>106.71</v>
       </c>
     </row>
     <row r="9">
@@ -478,7 +478,7 @@
         <v>Accounts Receivable</v>
       </c>
       <c r="D9">
-        <v>37451.81</v>
+        <v>36061.54</v>
       </c>
     </row>
     <row r="10">
@@ -492,7 +492,7 @@
         <v>Other Current Asset</v>
       </c>
       <c r="D10">
-        <v>2503.89</v>
+        <v>2410.94</v>
       </c>
     </row>
     <row r="11">
@@ -506,7 +506,7 @@
         <v>Other Current Asset</v>
       </c>
       <c r="D11">
-        <v>1967.04</v>
+        <v>1894.02</v>
       </c>
     </row>
     <row r="12">
@@ -520,7 +520,7 @@
         <v>Other Asset</v>
       </c>
       <c r="D12">
-        <v>4604.91</v>
+        <v>4433.97</v>
       </c>
     </row>
     <row r="13">
@@ -534,7 +534,7 @@
         <v>Fixed Asset</v>
       </c>
       <c r="D13">
-        <v>19409.54</v>
+        <v>18689.03</v>
       </c>
     </row>
     <row r="14">
@@ -548,7 +548,7 @@
         <v>Fixed Asset</v>
       </c>
       <c r="D14">
-        <v>-7177.31</v>
+        <v>-6910.87</v>
       </c>
     </row>
     <row r="15">
@@ -562,7 +562,7 @@
         <v>Other Asset</v>
       </c>
       <c r="D15">
-        <v>1205.6</v>
+        <v>1160.85</v>
       </c>
     </row>
     <row r="16">
@@ -576,7 +576,7 @@
         <v>Accounts Payable</v>
       </c>
       <c r="D16">
-        <v>-11030.99</v>
+        <v>-10621.5</v>
       </c>
     </row>
     <row r="17">
@@ -590,7 +590,7 @@
         <v>Other Current Liability</v>
       </c>
       <c r="D17">
-        <v>-5656.4</v>
+        <v>-5446.42</v>
       </c>
     </row>
     <row r="18">
@@ -604,7 +604,7 @@
         <v>Other Current Liability</v>
       </c>
       <c r="D18">
-        <v>-2720.32</v>
+        <v>-2619.34</v>
       </c>
     </row>
     <row r="19">
@@ -618,7 +618,7 @@
         <v>Other Current Liability</v>
       </c>
       <c r="D19">
-        <v>-2184.76</v>
+        <v>-2103.66</v>
       </c>
     </row>
     <row r="20">
@@ -632,7 +632,7 @@
         <v>Other Current Liability</v>
       </c>
       <c r="D20">
-        <v>-3239</v>
+        <v>-79427.81</v>
       </c>
     </row>
     <row r="21">
@@ -646,7 +646,7 @@
         <v>Equity</v>
       </c>
       <c r="D21">
-        <v>-47637</v>
+        <v>-150000</v>
       </c>
     </row>
     <row r="22">
@@ -660,7 +660,7 @@
         <v>Equity</v>
       </c>
       <c r="D22">
-        <v>-25431.68</v>
+        <v>-50000</v>
       </c>
     </row>
     <row r="23">
@@ -674,7 +674,7 @@
         <v>Equity</v>
       </c>
       <c r="D23">
-        <v>-13063.85</v>
+        <v>-12967.94</v>
       </c>
     </row>
     <row r="24">
@@ -688,7 +688,7 @@
         <v>Income</v>
       </c>
       <c r="D24">
-        <v>-96004.09</v>
+        <v>-124307.68</v>
       </c>
     </row>
     <row r="25">
@@ -702,7 +702,7 @@
         <v>Other Income</v>
       </c>
       <c r="D25">
-        <v>-604</v>
+        <v>-479.66</v>
       </c>
     </row>
     <row r="26">
@@ -716,7 +716,7 @@
         <v>Cost Of Goods Sold</v>
       </c>
       <c r="D26">
-        <v>34800.89</v>
+        <v>27636.31</v>
       </c>
     </row>
     <row r="27">
@@ -730,7 +730,7 @@
         <v>Expense</v>
       </c>
       <c r="D27">
-        <v>29985.05</v>
+        <v>23811.93</v>
       </c>
     </row>
     <row r="28">
@@ -744,7 +744,7 @@
         <v>Expense</v>
       </c>
       <c r="D28">
-        <v>2789.14</v>
+        <v>2214.94</v>
       </c>
     </row>
     <row r="29">
@@ -758,7 +758,7 @@
         <v>Expense</v>
       </c>
       <c r="D29">
-        <v>3937.99</v>
+        <v>3127.26</v>
       </c>
     </row>
     <row r="30">
@@ -772,7 +772,7 @@
         <v>Expense</v>
       </c>
       <c r="D30">
-        <v>3065.2</v>
+        <v>2434.16</v>
       </c>
     </row>
     <row r="31">
@@ -786,7 +786,7 @@
         <v>Expense</v>
       </c>
       <c r="D31">
-        <v>5034.45</v>
+        <v>3997.99</v>
       </c>
     </row>
     <row r="32">
@@ -800,7 +800,7 @@
         <v>Expense</v>
       </c>
       <c r="D32">
-        <v>1681.5</v>
+        <v>1335.32</v>
       </c>
     </row>
     <row r="33">
@@ -814,7 +814,7 @@
         <v>Expense</v>
       </c>
       <c r="D33">
-        <v>8137</v>
+        <v>33627.92</v>
       </c>
     </row>
     <row r="34">
@@ -828,7 +828,7 @@
         <v>Expense</v>
       </c>
       <c r="D34">
-        <v>3683.93</v>
+        <v>2925.5</v>
       </c>
     </row>
     <row r="35">

--- a/samples/Trial_Balance_UK_Jul-26.xlsx
+++ b/samples/Trial_Balance_UK_Jul-26.xlsx
@@ -450,7 +450,7 @@
         <v>Bank</v>
       </c>
       <c r="D7">
-        <v>279016.49</v>
+        <v>364372.54</v>
       </c>
     </row>
     <row r="8">
@@ -674,7 +674,7 @@
         <v>Equity</v>
       </c>
       <c r="D23">
-        <v>-12967.94</v>
+        <v>-95000</v>
       </c>
     </row>
     <row r="24">
@@ -688,7 +688,7 @@
         <v>Income</v>
       </c>
       <c r="D24">
-        <v>-124307.68</v>
+        <v>-87431.96</v>
       </c>
     </row>
     <row r="25">
@@ -702,7 +702,7 @@
         <v>Other Income</v>
       </c>
       <c r="D25">
-        <v>-479.66</v>
+        <v>-151.47</v>
       </c>
     </row>
     <row r="26">
@@ -716,7 +716,7 @@
         <v>Cost Of Goods Sold</v>
       </c>
       <c r="D26">
-        <v>27636.31</v>
+        <v>8275.8</v>
       </c>
     </row>
     <row r="27">
@@ -730,7 +730,7 @@
         <v>Expense</v>
       </c>
       <c r="D27">
-        <v>23811.93</v>
+        <v>7151.12</v>
       </c>
     </row>
     <row r="28">
@@ -744,7 +744,7 @@
         <v>Expense</v>
       </c>
       <c r="D28">
-        <v>2214.94</v>
+        <v>664.48</v>
       </c>
     </row>
     <row r="29">
@@ -758,7 +758,7 @@
         <v>Expense</v>
       </c>
       <c r="D29">
-        <v>3127.26</v>
+        <v>938.18</v>
       </c>
     </row>
     <row r="30">
@@ -772,7 +772,7 @@
         <v>Expense</v>
       </c>
       <c r="D30">
-        <v>2434.16</v>
+        <v>722.72</v>
       </c>
     </row>
     <row r="31">
@@ -786,7 +786,7 @@
         <v>Expense</v>
       </c>
       <c r="D31">
-        <v>3997.99</v>
+        <v>1206.94</v>
       </c>
     </row>
     <row r="32">
@@ -800,7 +800,7 @@
         <v>Expense</v>
       </c>
       <c r="D32">
-        <v>1335.32</v>
+        <v>393.04</v>
       </c>
     </row>
     <row r="33">
@@ -814,7 +814,7 @@
         <v>Expense</v>
       </c>
       <c r="D33">
-        <v>33627.92</v>
+        <v>40353.5</v>
       </c>
     </row>
     <row r="34">
@@ -828,7 +828,7 @@
         <v>Expense</v>
       </c>
       <c r="D34">
-        <v>2925.5</v>
+        <v>877.65</v>
       </c>
     </row>
     <row r="35">

--- a/samples/Trial_Balance_UK_Jul-26.xlsx
+++ b/samples/Trial_Balance_UK_Jul-26.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D35"/>
+  <dimension ref="A1:D34"/>
   <cols>
     <col min="1" max="1" width="14.83203125" customWidth="1"/>
     <col min="2" max="2" width="52.83203125" customWidth="1"/>
@@ -450,7 +450,7 @@
         <v>Bank</v>
       </c>
       <c r="D7">
-        <v>364372.54</v>
+        <v>396897.86</v>
       </c>
     </row>
     <row r="8">
@@ -464,7 +464,7 @@
         <v>Cash</v>
       </c>
       <c r="D8">
-        <v>106.71</v>
+        <v>101.65</v>
       </c>
     </row>
     <row r="9">
@@ -478,7 +478,7 @@
         <v>Accounts Receivable</v>
       </c>
       <c r="D9">
-        <v>36061.54</v>
+        <v>34350.9</v>
       </c>
     </row>
     <row r="10">
@@ -492,7 +492,7 @@
         <v>Other Current Asset</v>
       </c>
       <c r="D10">
-        <v>2410.94</v>
+        <v>2296.57</v>
       </c>
     </row>
     <row r="11">
@@ -506,7 +506,7 @@
         <v>Other Current Asset</v>
       </c>
       <c r="D11">
-        <v>1894.02</v>
+        <v>1804.17</v>
       </c>
     </row>
     <row r="12">
@@ -520,7 +520,7 @@
         <v>Other Asset</v>
       </c>
       <c r="D12">
-        <v>4433.97</v>
+        <v>4223.63</v>
       </c>
     </row>
     <row r="13">
@@ -534,7 +534,7 @@
         <v>Fixed Asset</v>
       </c>
       <c r="D13">
-        <v>18689.03</v>
+        <v>17802.48</v>
       </c>
     </row>
     <row r="14">
@@ -548,7 +548,7 @@
         <v>Fixed Asset</v>
       </c>
       <c r="D14">
-        <v>-6910.87</v>
+        <v>-6583.04</v>
       </c>
     </row>
     <row r="15">
@@ -562,7 +562,7 @@
         <v>Other Asset</v>
       </c>
       <c r="D15">
-        <v>1160.85</v>
+        <v>1105.78</v>
       </c>
     </row>
     <row r="16">
@@ -576,7 +576,7 @@
         <v>Accounts Payable</v>
       </c>
       <c r="D16">
-        <v>-10621.5</v>
+        <v>-44653</v>
       </c>
     </row>
     <row r="17">
@@ -590,7 +590,7 @@
         <v>Other Current Liability</v>
       </c>
       <c r="D17">
-        <v>-5446.42</v>
+        <v>-5188.06</v>
       </c>
     </row>
     <row r="18">
@@ -604,7 +604,7 @@
         <v>Other Current Liability</v>
       </c>
       <c r="D18">
-        <v>-2619.34</v>
+        <v>-2495.08</v>
       </c>
     </row>
     <row r="19">
@@ -618,7 +618,7 @@
         <v>Other Current Liability</v>
       </c>
       <c r="D19">
-        <v>-2103.66</v>
+        <v>-2003.86</v>
       </c>
     </row>
     <row r="20">
@@ -632,7 +632,7 @@
         <v>Other Current Liability</v>
       </c>
       <c r="D20">
-        <v>-79427.81</v>
+        <v>-75660</v>
       </c>
     </row>
     <row r="21">
@@ -646,202 +646,188 @@
         <v>Equity</v>
       </c>
       <c r="D21">
-        <v>-150000</v>
+        <v>-200000</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>3100</v>
+        <v>3200</v>
       </c>
       <c r="B22" t="str">
-        <v>Securities Premium</v>
+        <v>Retained Earnings</v>
       </c>
       <c r="C22" t="str">
         <v>Equity</v>
       </c>
       <c r="D22">
-        <v>-50000</v>
+        <v>-95000</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>3200</v>
+        <v>4001</v>
       </c>
       <c r="B23" t="str">
-        <v>Retained Earnings</v>
+        <v>Consulting Revenue</v>
       </c>
       <c r="C23" t="str">
-        <v>Equity</v>
+        <v>Income</v>
       </c>
       <c r="D23">
-        <v>-95000</v>
+        <v>-84525.98</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>4001</v>
+        <v>4500</v>
       </c>
       <c r="B24" t="str">
-        <v>Consulting Revenue</v>
+        <v>Interest Income</v>
       </c>
       <c r="C24" t="str">
-        <v>Income</v>
+        <v>Other Income</v>
       </c>
       <c r="D24">
-        <v>-87431.96</v>
+        <v>-144.29</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>4500</v>
+        <v>5001</v>
       </c>
       <c r="B25" t="str">
-        <v>Interest Income</v>
+        <v>Cost of Services</v>
       </c>
       <c r="C25" t="str">
-        <v>Other Income</v>
+        <v>Cost Of Goods Sold</v>
       </c>
       <c r="D25">
-        <v>-151.47</v>
+        <v>7883.21</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>5001</v>
+        <v>6001</v>
       </c>
       <c r="B26" t="str">
-        <v>Cost of Services</v>
+        <v>Salaries and Wages</v>
       </c>
       <c r="C26" t="str">
-        <v>Cost Of Goods Sold</v>
+        <v>Expense</v>
       </c>
       <c r="D26">
-        <v>8275.8</v>
+        <v>6811.89</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>6001</v>
+        <v>6100</v>
       </c>
       <c r="B27" t="str">
-        <v>Salaries and Wages</v>
+        <v>Travel and Conveyance</v>
       </c>
       <c r="C27" t="str">
         <v>Expense</v>
       </c>
       <c r="D27">
-        <v>7151.12</v>
+        <v>632.95</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>6100</v>
+        <v>6200</v>
       </c>
       <c r="B28" t="str">
-        <v>Travel and Conveyance</v>
+        <v>Professional Fees</v>
       </c>
       <c r="C28" t="str">
         <v>Expense</v>
       </c>
       <c r="D28">
-        <v>664.48</v>
+        <v>893.68</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>6200</v>
+        <v>6300</v>
       </c>
       <c r="B29" t="str">
-        <v>Professional Fees</v>
+        <v>Software Subscriptions</v>
       </c>
       <c r="C29" t="str">
         <v>Expense</v>
       </c>
       <c r="D29">
-        <v>938.18</v>
+        <v>688.44</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>6300</v>
+        <v>6400</v>
       </c>
       <c r="B30" t="str">
-        <v>Software Subscriptions</v>
+        <v>Rent</v>
       </c>
       <c r="C30" t="str">
         <v>Expense</v>
       </c>
       <c r="D30">
-        <v>722.72</v>
+        <v>1149.69</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>6400</v>
+        <v>6500</v>
       </c>
       <c r="B31" t="str">
-        <v>Rent</v>
+        <v>Depreciation</v>
       </c>
       <c r="C31" t="str">
         <v>Expense</v>
       </c>
       <c r="D31">
-        <v>1206.94</v>
+        <v>374.39</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>6500</v>
+        <v>6600</v>
       </c>
       <c r="B32" t="str">
-        <v>Depreciation</v>
+        <v>IC Service Charges - India</v>
       </c>
       <c r="C32" t="str">
         <v>Expense</v>
       </c>
       <c r="D32">
-        <v>393.04</v>
+        <v>38400</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>6600</v>
+        <v>6900</v>
       </c>
       <c r="B33" t="str">
-        <v>IC Service Charges - India</v>
+        <v>Income Tax Expense</v>
       </c>
       <c r="C33" t="str">
         <v>Expense</v>
       </c>
       <c r="D33">
-        <v>40353.5</v>
+        <v>836.02</v>
       </c>
     </row>
     <row r="34">
-      <c r="A34" t="str">
-        <v>6900</v>
-      </c>
       <c r="B34" t="str">
-        <v>Income Tax Expense</v>
-      </c>
-      <c r="C34" t="str">
-        <v>Expense</v>
+        <v>Total</v>
       </c>
       <c r="D34">
-        <v>877.65</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="B35" t="str">
-        <v>Total</v>
-      </c>
-      <c r="D35">
         <v>0</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D35"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D34"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/samples/Trial_Balance_UK_Jul-26.xlsx
+++ b/samples/Trial_Balance_UK_Jul-26.xlsx
@@ -450,7 +450,7 @@
         <v>Bank</v>
       </c>
       <c r="D7">
-        <v>396897.86</v>
+        <v>299608.98</v>
       </c>
     </row>
     <row r="8">
@@ -576,7 +576,7 @@
         <v>Accounts Payable</v>
       </c>
       <c r="D16">
-        <v>-44653</v>
+        <v>-10117.65</v>
       </c>
     </row>
     <row r="17">
@@ -674,7 +674,7 @@
         <v>Income</v>
       </c>
       <c r="D23">
-        <v>-84525.98</v>
+        <v>-21772.45</v>
       </c>
     </row>
     <row r="24">
@@ -730,7 +730,7 @@
         <v>Expense</v>
       </c>
       <c r="D27">
-        <v>632.95</v>
+        <v>632.96</v>
       </c>
     </row>
     <row r="28">
@@ -744,7 +744,7 @@
         <v>Expense</v>
       </c>
       <c r="D28">
-        <v>893.68</v>
+        <v>893.67</v>
       </c>
     </row>
     <row r="29">
